--- a/output/all_teachers_orar.xlsx
+++ b/output/all_teachers_orar.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="1" r:id="R135e4eadb9134e9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="1" r:id="R025498663fd54f23"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -40,15 +40,33 @@
     <x:t>L. str. 222/4</x:t>
   </x:si>
   <x:si>
+    <x:t>Progr. C++ (lab) 143/4 DJ2502-I</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA2D (lab) 251/4 I2502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Intel. artif. (lab) 423/4 DJ2502-II (impar)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tehn. progr. (curs) 404/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (lab) 237/4 IA2601-I</x:t>
   </x:si>
   <x:si>
     <x:t>Fund. progr. (curs) 214/4 M2601</x:t>
   </x:si>
   <x:si>
+    <x:t>GA2D (curs) 213a/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (sem) 401/4 IA2604</x:t>
   </x:si>
   <x:si>
+    <x:t>DCMIMJ (lab) 350/4 DJ2502-I</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (lab) 145/4 DJ2601</x:t>
   </x:si>
   <x:si>
@@ -58,6 +76,15 @@
     <x:t>Matem. (sem) 113/4 IA2603</x:t>
   </x:si>
   <x:si>
+    <x:t>Intel. artif. (lab) 423/4 DJ2502-II</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Desig. UI/UX (lab) 326/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tehn. progr. (curs) 218/4 DU-IA2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sec. ciber. (lab) 145/4 IA2604-II</x:t>
   </x:si>
   <x:si>
@@ -70,28 +97,67 @@
     <x:t>Fund. progr. (lab) 143/4 M2601</x:t>
   </x:si>
   <x:si>
+    <x:t>GA2D (lab) 218/4a</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (sem) 401/4 IA2603</x:t>
   </x:si>
   <x:si>
+    <x:t>Intel. artif. (lab) 350/4 DJ2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designul UI/U X (curs) 419/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (curs) 214/4</x:t>
   </x:si>
   <x:si>
+    <x:t>GA2D (curs) 404/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sec. ciber. (lab) 145a/4 IA2602</x:t>
   </x:si>
   <x:si>
     <x:t>Matem. (sem) 113/4 I2602</x:t>
   </x:si>
   <x:si>
+    <x:t>Intel. artif. (lab) 423/4 DJ2502-I</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dezv. WEB. (lab) 326/4 I2502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Desig. UI/UX (curs) 213a/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (lab) 145/4 IA2603-I</x:t>
   </x:si>
   <x:si>
     <x:t>Fund. progr. (lab) 237/4 IA2601-II</x:t>
   </x:si>
   <x:si>
+    <x:t>Intel. artif. (curs) 218/4 DU-IA2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA2D (lab) 218/4a (par)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCMIMJ (lab) 350/4 DJ2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Desig. UI/UX (curs) 145a/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fund. progr. (sem) 214/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA2D (lab) 251/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Matem. (sem) 113/4 IA2604</x:t>
   </x:si>
   <x:si>
-    <x:t>Fund. progr. (sem) 214/4</x:t>
+    <x:t>Intel. artif. (lab) 423/4 DJ2502-I (par)</x:t>
   </x:si>
   <x:si>
     <x:t>L. str. 419/4 I2602</x:t>
@@ -100,15 +166,25 @@
     <x:t>Sec. ciber. (lab) 145/4 IA2603-I</x:t>
   </x:si>
   <x:si>
+    <x:t>DCMIMJ (lab) 350/4 DJ2501 (impar)
+Intel. artif. (lab) 350/4 DJ2501 (par)</x:t>
+  </x:si>
+  <x:si>
     <x:t>GA2D (curs) 214/4</x:t>
   </x:si>
   <x:si>
+    <x:t>Desig. UI/UX (lab) 326/4 (par)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Design nar. (sem) 404/4 DJ2602</x:t>
   </x:si>
   <x:si>
     <x:t>PSI (lab) 143/4 DU-IA2601 (par)</x:t>
   </x:si>
   <x:si>
+    <x:t>Teor. probab. (curs) 222/4 M2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sist. de oper. (curs) 213a/4</x:t>
   </x:si>
   <x:si>
@@ -124,31 +200,81 @@
     <x:t>Sist. de oper. (lab) 251/4 IA2603-I</x:t>
   </x:si>
   <x:si>
+    <x:t>Cript. și SI (lab) 145/4 DU-IA2501 (impar)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Design nar. (curs) 404/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Progr. C++ (lab) 423/4 DJ2501 (impar)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Logica și teor. mulț. (curs) 415/4 M2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Progr. C++ (lab) 143/4 DJ2503-eng (impar)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (sem) 214/4 I2602</x:t>
   </x:si>
   <x:si>
-    <x:t>Design nar. (curs) 404/4</x:t>
+    <x:t>Tehn. progr. (curs) 213a/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCMIMJ (lab) 350/4 DJ2503-eng (par)</x:t>
   </x:si>
   <x:si>
     <x:t>PSI (curs) 419/4 DU-IA2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Teor. probab. (sem) 222/4 M2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sist. de oper. (curs) 113/4</x:t>
   </x:si>
   <x:si>
+    <x:t>BD (lab) 237/4 IA2502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tehn. progr. (lab) 145/4 IA2503</x:t>
+  </x:si>
+  <x:si>
     <x:t>L. str. 401/4</x:t>
   </x:si>
   <x:si>
+    <x:t>Cript. și SI (curs) 404/4 (impar)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Matem. (curs) 113/4</x:t>
   </x:si>
   <x:si>
+    <x:t>Progr. C++ (lab) 423/4 DJ2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Logica și teor. mulț. (sem) 415/4 M2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Progr. C++ (lab) 143/4 DJ2503-eng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POO (curs) 214/4 M2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA2D (lab) 251/4 I2502 (impar)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (curs) 213a/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCMIMJ (lab) 350/4 DJ2502-II</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BD (lab) 237/4
+impar: DU-IA2501
+par: I2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BD (lab) 326/4 IA2504</x:t>
   </x:si>
   <x:si>
     <x:t>HTML (lab) 145a/4 DU-IA2601 (par)</x:t>
@@ -165,6 +291,12 @@
 par: I2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Progr. C++ (lab) 143/4 DJ2502-II</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disciplină umanistică opțională: Antreprenoriat inovativ (curs) 528/3</x:t>
+  </x:si>
+  <x:si>
     <x:t>VSDG (lab) 350/4 DJ2602-II (par)</x:t>
   </x:si>
   <x:si>
@@ -173,33 +305,68 @@
 impar: I2602</x:t>
   </x:si>
   <x:si>
+    <x:t>Antreprenoriat inovativ (curs) 528/3</x:t>
+  </x:si>
+  <x:si>
     <x:t>HTML (lab) 251/4 IA2603-I</x:t>
   </x:si>
   <x:si>
     <x:t>HTML (lab) 145a/4 IA2603-II</x:t>
   </x:si>
   <x:si>
+    <x:t>Ps. (curs) 401/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Matem. (sem) 404/4 IA2602 (par)</x:t>
   </x:si>
   <x:si>
+    <x:t>Dezv. WEB. (lab) 145a/4 I2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ps. (sem) 401/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>L. str. 222/4 IA2603</x:t>
   </x:si>
   <x:si>
+    <x:t>BD (lab) 218/4a IA2501 (par)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (sem) 401/4</x:t>
   </x:si>
   <x:si>
+    <x:t>GA2D (lab) 251/4 (impar)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (sem) 214/4 IA2602</x:t>
   </x:si>
   <x:si>
     <x:t>Sec. ciber. (lab) 145a/4 DU-IA2601 (impar)</x:t>
   </x:si>
   <x:si>
+    <x:t>Intel. artif. (lab) 143/4 DU-IA2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>L. str. 415/4</x:t>
   </x:si>
   <x:si>
+    <x:t>Cript. și SI (lab) 143/4
+impar: IA2502
+par: DU-IA2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cript. și SI (curs) 401/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Matem. (sem) 404/4 I2601</x:t>
   </x:si>
   <x:si>
+    <x:t>IA p/u JV (curs) 113/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BD (lab) 218/4a IA2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sec. ciber. (curs) 213a/4</x:t>
   </x:si>
   <x:si>
@@ -209,9 +376,23 @@
     <x:t>Fund. progr. (sem) 214/4 IA2601</x:t>
   </x:si>
   <x:si>
+    <x:t>BD (lab) 237/4 I2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Metode de optim. (curs) 218/4 M2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tehn. progr. (lab) 216a/4a DU-IA2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (lab) 237/4 IA2603-II</x:t>
   </x:si>
   <x:si>
+    <x:t>Cript. și SI (lab) 143/4
+impar: IA2501
+par: I2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>L. str. 222/4 IA2601 (par)</x:t>
   </x:si>
   <x:si>
@@ -221,15 +402,22 @@
     <x:t>Matem. (sem) 404/4 IA2602</x:t>
   </x:si>
   <x:si>
+    <x:t>Progr. C++ (curs) 423/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>VSDG (lab) 350/4 DJ2602-II</x:t>
   </x:si>
   <x:si>
-    <x:t>Sist. de oper. (lab) 218/4a IA2601-I (impar)</x:t>
+    <x:t>Sist. de oper. (lab) 218/4a IA2601-I (impar)
+Tehn. progr. (lab) 218/4a IA2501 (par)</x:t>
   </x:si>
   <x:si>
     <x:t>HTML (lab) 326/4 I2602</x:t>
   </x:si>
   <x:si>
+    <x:t>Dezv. WEB avan. (curs) 213a/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (lab) 145a/4 DJ2602-I</x:t>
   </x:si>
   <x:si>
@@ -245,12 +433,21 @@
     <x:t>Matem. (curs) 415/4 DU-IA2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Metode de optim. (sem) 218/4 M2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dezv. WEB. (lab) 219/4a IA2502</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sec. ciber. (lab) 237/4 IA2603-II</x:t>
   </x:si>
   <x:si>
     <x:t>Matem. (sem) 404/4 IA2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Antreprenoriat inovativ (sem) 218/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>VSDG (lab) 350/4 DJ2602-I</x:t>
   </x:si>
   <x:si>
@@ -263,18 +460,36 @@
     <x:t>Fund. progr. (lab) 145a/4 DJ2602-II</x:t>
   </x:si>
   <x:si>
+    <x:t>Disciplină umanistică opțională: Antreprenoriat inovativ (sem) 401/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DJ3DU (lab) 423/4 DJ2502-I</x:t>
+  </x:si>
+  <x:si>
     <x:t>GA2D (lab) 251/4 DJ2601 (impar)</x:t>
   </x:si>
   <x:si>
     <x:t>Matem. (sem) 415/4 DU-IA2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Antreprenoriat inovativ (sem) 214/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>HTML (lab) 218/4a IA2604-I</x:t>
   </x:si>
   <x:si>
     <x:t>HTML (lab) 219/4a IA2604-II</x:t>
   </x:si>
   <x:si>
+    <x:t>Criptogr. (lab) 145/4 IA2503</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Antrepren. (sem) 404/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ped. (curs) 433/3</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sist. de oper. (lab) 237/4 IA2604-II</x:t>
   </x:si>
   <x:si>
@@ -284,9 +499,21 @@
     <x:t>GA2D (lab) 143/4 DJ2602-I (impar)</x:t>
   </x:si>
   <x:si>
+    <x:t>DJ3DU (lab) 423/4 DJ2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Desig. UI/UX (lab) 145a/4 (impar)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BD (curs) 404/4 DU-IA2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sec. ciber. (curs) 419/4 DU-IA2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Tehn. progr. (lab) 219/4a IA2504</x:t>
+  </x:si>
+  <x:si>
     <x:t>Limba rom. 401/4 IA2604</x:t>
   </x:si>
   <x:si>
@@ -296,9 +523,15 @@
     <x:t>Sist. de oper. (lab) 350/4 IA2603-I (par)</x:t>
   </x:si>
   <x:si>
+    <x:t>Cript. și SI (curs) 145/4 DU-IA2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (lab) 251/4 I2602</x:t>
   </x:si>
   <x:si>
+    <x:t>Geom. dif. (curs) 214/4 M2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>GA2D (lab) 143/4 DJ2602-I</x:t>
   </x:si>
   <x:si>
@@ -311,57 +544,111 @@
     <x:t>Sist. de oper. (lab) 326/4 IA2602</x:t>
   </x:si>
   <x:si>
+    <x:t>BD (curs) 404/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Algebra liniară (curs) 415/4 M2601</x:t>
   </x:si>
   <x:si>
     <x:t>Sist. de oper. (curs) 419/4 DU-IA2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Dezv. WEB. (lab) 218/4a IA2503</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tehn. progr. (lab) 219/4a I2502</x:t>
+  </x:si>
+  <x:si>
     <x:t>Limba rom. 401/4 IA2603</x:t>
   </x:si>
   <x:si>
     <x:t>Sist. de oper. (lab) 237/4 IA2604-I</x:t>
   </x:si>
   <x:si>
+    <x:t>Cript. și SI (lab) 145/4 DU-IA2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (lab) 251/4 IA2604-II</x:t>
   </x:si>
   <x:si>
+    <x:t>) 143/4 DJ2502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Geom. dif. (sem) 214/4 M2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>GA2D (curs) 419/4</x:t>
   </x:si>
   <x:si>
+    <x:t>DJ3DU (curs) 423/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>) 350/4 DJ2502</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sist. de oper. (lab) 145a/4 DU-IA2601</x:t>
   </x:si>
   <x:si>
     <x:t>Sist. de oper. (lab) 326/4 I2602</x:t>
   </x:si>
   <x:si>
+    <x:t>Dezv. WEB avan. (curs) 404/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Algebra liniară (sem) 415/4 M2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Dezv. WEB. (lab) 218/4a IA2504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ps. (sem) 404/4 (impar)</x:t>
+  </x:si>
+  <x:si>
     <x:t>L. str. 214/4 IA2604</x:t>
   </x:si>
   <x:si>
+    <x:t>Ped. (sem) 433/3</x:t>
+  </x:si>
+  <x:si>
     <x:t>Limba rom. 401/4</x:t>
   </x:si>
   <x:si>
     <x:t>VSDG (curs) 145/4</x:t>
   </x:si>
   <x:si>
+    <x:t>Antreprenoriat inovativ (sem) 419/4 (par)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (lab) 251/4 DU-IA2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Progr. C++ (curs) 254/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>VSDG (lab) 350/4 DJ2602-I (impar)</x:t>
   </x:si>
   <x:si>
     <x:t>Sec. ciber. (lab) 145a/4 I2602</x:t>
   </x:si>
   <x:si>
+    <x:t>Disciplină umanistică opțională: Antreprenoriat inovativ (sem) 214 (par)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Calc. difer. și int. (sem) 419/4 M2601 (impar)</x:t>
   </x:si>
   <x:si>
+    <x:t>Antreprenoriat inovativ (sem) 415/4 (par)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ps. (sem) 404/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Limba rom. 401/4 I2602 (par)</x:t>
   </x:si>
   <x:si>
+    <x:t>Ped. (sem) 433/3 (impar)</x:t>
+  </x:si>
+  <x:si>
     <x:t>VSDG (lab) 145/4 DJ2601</x:t>
   </x:si>
   <x:si>
@@ -371,19 +658,34 @@
     <x:t>HTML (lab) 237/4 IA2601-I</x:t>
   </x:si>
   <x:si>
+    <x:t>Criptogr. (lab) 326/4 IA2504</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sist. de oper. (lab) 145a/4 IA2601-II</x:t>
   </x:si>
   <x:si>
+    <x:t>Ped. (curs) 433/3 (par)</x:t>
+  </x:si>
+  <x:si>
     <x:t>VSDG (lab) 145/4 DJ2601 (impar)</x:t>
   </x:si>
   <x:si>
     <x:t>HTML (lab) 237/4 IA2601-II</x:t>
   </x:si>
   <x:si>
+    <x:t>Criptogr. (lab) 326/4 IA2504 (impar)</x:t>
+  </x:si>
+  <x:si>
     <x:t>L. str. 222/4 (par)</x:t>
   </x:si>
   <x:si>
+    <x:t>DCMIMJ (lab) 350/4 DJ2503-eng</x:t>
+  </x:si>
+  <x:si>
     <x:t>HTML (curs) 113/4 DU-IA2601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teor. probab. (lab) 143/4 M2501 (impar)</x:t>
   </x:si>
   <x:si>
     <x:t>Matem. (sem) 214/4
@@ -394,53 +696,110 @@
     <x:t>Sec. ciber. (lab) 145a/4 IA2601-II</x:t>
   </x:si>
   <x:si>
+    <x:t>Intel. artif. (lab) 145/4 DU-IA2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BD (lab) 326/4 IA2503</x:t>
+  </x:si>
+  <x:si>
     <x:t>Rețele de calcul. (curs) 145a/4 DU-IA2601</x:t>
   </x:si>
   <x:si>
     <x:t>Geom. analit. (curs) 415/4 M2601</x:t>
   </x:si>
   <x:si>
+    <x:t>POO (lab) 143/4 M2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tehn. progr. (lab) 237/4 IA2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Antrepren. (curs) 214/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fund. progr. (curs) 404/4</x:t>
   </x:si>
   <x:si>
     <x:t>HTML (curs) 113a/4</x:t>
   </x:si>
   <x:si>
+    <x:t>Dezv. WEB avan. (curs) 419/4 DU-IA2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Matem. (curs) 213a/4</x:t>
   </x:si>
   <x:si>
+    <x:t>BD (curs) 401/4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tehn. progr. (lab) 219/4a
+impar: IA2504
+par: I2502</x:t>
+  </x:si>
+  <x:si>
     <x:t>Rețele de calcul. (lab) 145a/4 DU-IA2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Cript. și SI (curs) 113/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Geom. analit. (sem) 415/4 M2601</x:t>
   </x:si>
   <x:si>
     <x:t>Fund. progr. (lab) 251/4 IA2602</x:t>
   </x:si>
   <x:si>
+    <x:t>Ecuații difer. (curs) 404/4 M2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCIMJ (curs) 419/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sist. de oper. (lab) 237/4 IA2601-I</x:t>
   </x:si>
   <x:si>
+    <x:t>Antrepren. (sem) 214/4</x:t>
+  </x:si>
+  <x:si>
     <x:t>HTML (curs) 213a/4</x:t>
   </x:si>
   <x:si>
     <x:t>HTML (lab) 143/4 I2601</x:t>
   </x:si>
   <x:si>
+    <x:t>BD (lab) 145/4 DU-IA2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BD (lab) 218/4a
+: I2502
+par: IA2503</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tehn. progr. (lab) 219/4a IA2503 (par)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Limba rom. 401/4 I2602</x:t>
   </x:si>
   <x:si>
     <x:t>Rețele de calcul. (lab) 145a/4 DU-IA2601 (par)</x:t>
   </x:si>
   <x:si>
+    <x:t>Cript. și SI (lab) 145/4 I2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cript. și SI (curs) 113/4 (impar)</x:t>
+  </x:si>
+  <x:si>
     <x:t>L. str. 222/4 (impar)</x:t>
   </x:si>
   <x:si>
     <x:t>Proiect. JV (curs) 419/4</x:t>
   </x:si>
   <x:si>
-    <x:t>Geom. analit. (sem) 415/4 M2601 (impar)
-Matem. (sem) 222/4 IA2604 (par)</x:t>
+    <x:t>Geom. analit. (sem) 415/4 M2601 (impar)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ecuații difer. (sem) 404/4 M2501</x:t>
   </x:si>
   <x:si>
     <x:t>VSDG (curs) 214/4</x:t>
@@ -451,16 +810,62 @@
 par: IA2601</x:t>
   </x:si>
   <x:si>
+    <x:t>Dezv. WEB avan. (lab) 251/4 DU-IA2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DJ3DU (lab) 423/4 DJ2502-II</x:t>
+  </x:si>
+  <x:si>
     <x:t>Algebra liniară (sem) 415/4 M2601 (par)</x:t>
   </x:si>
   <x:si>
+    <x:t>Tehn. progr. (lab) 143/4 IA2502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Matem. (sem) 222/4 IA2604 (par)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Intel. artif. (lab) 145a/4 DJ2503-eng (impar)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BD (lab) 218/4a I2502 (par)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dezv. WEB. (lab) 326/4 IA2501</x:t>
+  </x:si>
+  <x:si>
     <x:t>Limba rom. 401/4 IA2604 (par)</x:t>
   </x:si>
   <x:si>
+    <x:t>Cript. și SI (lab) 145/4 IA2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tehn. progr. (lab) 237/4 I2501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Criptogr. (lab) 326/4 I2502 (impar)</x:t>
+  </x:si>
+  <x:si>
     <x:t>VSDG (lab) 350/4 DJ2603-eng</x:t>
   </x:si>
   <x:si>
+    <x:t>BD (lab) 143/4 IA2502 (impar)
+Tehn. progr. (lab) 143/4 IA2502 (par)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cript. și SI (lab) 145/4 IA2502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tehn. progr. (lab) 237/4 I2501 (impar)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Criptogr. (lab) 326/4 I2502</x:t>
+  </x:si>
+  <x:si>
     <x:t>Proiect. JV (lab) 143/4 DJ2601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analiza funcț. (curs) 214/4 M2501</x:t>
   </x:si>
   <x:si>
     <x:t>GA2D (lab) 237/4
@@ -468,7 +873,16 @@
 par: DJ2602</x:t>
   </x:si>
   <x:si>
+    <x:t>Intel. artif. (lab) 423/4 DJ2503-eng</x:t>
+  </x:si>
+  <x:si>
     <x:t>Design nar. (sem) 419/4 DJ2601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DJ3DU (lab) 423/4 DJ2503-eng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analiza funcț. (sem) 214/4 M2501</x:t>
   </x:si>
   <x:si>
     <x:t>GA2D (lab) 237/4 DJ2603-eng</x:t>
@@ -632,7 +1046,7 @@
   <x:cols>
     <x:col min="1" max="1" width="3.9515624999999996" customWidth="1"/>
     <x:col min="2" max="2" width="11.854687499999999" customWidth="1"/>
-    <x:col min="3" max="42" width="13.171875" customWidth="1"/>
+    <x:col min="3" max="66" width="13.171875" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row>
@@ -642,15 +1056,27 @@
    Ora</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Anghelova Irina</x:v>
+      </x:c>
+      <x:c s="3" t="str">
+        <x:v>Anțibor D.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Bașirov O.</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Bîrnaz N.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Boicenco A.</x:v>
       </x:c>
       <x:c s="3" t="str">
         <x:v>Borș Dumitru</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Butnari N.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Butnaru Mariana</x:v>
       </x:c>
       <x:c s="3" t="str">
@@ -660,6 +1086,9 @@
         <x:v>Capcelea Titu</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Cerbu Olga</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Ciudin G.</x:v>
       </x:c>
       <x:c s="3" t="str">
@@ -669,27 +1098,51 @@
         <x:v>Coșeru S.</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Costoglo L.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
+        <x:v>Croitor Mihail</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Crudu Cristian</x:v>
       </x:c>
       <x:c s="3" t="str">
         <x:v>Cucu I.</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Curmanscii A.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Damian F.</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Dobrovolschi I.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Donu Alexandru</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Efros P.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Grigorcea Viorel</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Guțu V.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Iațâșina Tamara</x:v>
       </x:c>
       <x:c s="3" t="str">
         <x:v>Isac J.</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Jelascov I.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
+        <x:v>Jelihovschii Vladimir</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Latul Gheorghe</x:v>
       </x:c>
       <x:c s="3" t="str">
@@ -702,15 +1155,24 @@
         <x:v>Marin Ghenadie</x:v>
       </x:c>
       <x:c s="3" t="str">
-        <x:v>Murea E.</x:v>
+        <x:v>Mîndru Eugen</x:v>
+      </x:c>
+      <x:c s="3" t="str">
+        <x:v>Mulic A.</x:v>
       </x:c>
       <x:c s="3" t="str">
         <x:v>Nartea Nichita</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Nazar N.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Negură Denis</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Nepotu L.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Novac Ludmila</x:v>
       </x:c>
       <x:c s="3" t="str">
@@ -723,12 +1185,24 @@
         <x:v>Pleșca Natalia</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Popa V.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
+        <x:v>Pugaci Diana</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Râbacova G.</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Rusu G.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Sârbu P.</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Șargu L.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Șchiopu Alina</x:v>
       </x:c>
       <x:c s="3" t="str">
@@ -747,10 +1221,22 @@
         <x:v>Sprinceanu G.</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Stoler D.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Tican Ion</x:v>
       </x:c>
       <x:c s="3" t="str">
+        <x:v>Tkacenko A.</x:v>
+      </x:c>
+      <x:c s="3" t="str">
         <x:v>Tretiacova Elizaveta</x:v>
+      </x:c>
+      <x:c s="3" t="str">
+        <x:v>Ulmanu Cristian</x:v>
+      </x:c>
+      <x:c s="3" t="str">
+        <x:v>Valic M.</x:v>
       </x:c>
       <x:c s="3" t="str">
         <x:v>Vișnevschii Boris</x:v>
@@ -768,12 +1254,17 @@
       </x:c>
       <x:c s="4"/>
       <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
       <x:c s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
       <x:c s="4" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -783,28 +1274,53 @@
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
-      <x:c s="4"/>
+      <x:c s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
@@ -815,6 +1331,13 @@
       <x:c s="15" t="s">
         <x:v>2</x:v>
       </x:c>
+      <x:c s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
@@ -826,109 +1349,176 @@
       </x:c>
       <x:c s="6"/>
       <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
       <x:c s="6" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="1"/>
       <x:c s="15" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>39</x:v>
+      </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="1"/>
@@ -937,9 +1527,14 @@
       </x:c>
       <x:c s="6"/>
       <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>24</x:v>
-      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
@@ -948,93 +1543,154 @@
       </x:c>
       <x:c s="6"/>
       <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="1"/>
       <x:c s="15" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c s="6" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>54</x:v>
+      </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="1"/>
@@ -1080,6 +1736,30 @@
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="1"/>
@@ -1125,6 +1805,30 @@
       <x:c s="5"/>
       <x:c s="5"/>
       <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="2" t="str">
@@ -1145,38 +1849,64 @@
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
       <x:c s="7" t="s">
-        <x:v>31</x:v>
-      </x:c>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
+        <x:v>56</x:v>
+      </x:c>
       <x:c s="7" t="s">
-        <x:v>33</x:v>
-      </x:c>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7" t="s">
-        <x:v>34</x:v>
-      </x:c>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
@@ -1186,53 +1916,91 @@
       <x:c s="18" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c s="9" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>42</x:v>
-      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
@@ -1248,53 +2016,95 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
@@ -1302,60 +2112,90 @@
       <x:c s="18" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c s="9" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>54</x:v>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
@@ -1364,46 +2204,74 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>101</x:v>
+      </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="2"/>
@@ -1411,6 +2279,32 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
@@ -1494,6 +2388,30 @@
       <x:c s="8"/>
       <x:c s="8"/>
       <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="1" t="str">
@@ -1508,9 +2426,18 @@
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
       <x:c s="4" t="s">
-        <x:v>56</x:v>
-      </x:c>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
@@ -1527,25 +2454,46 @@
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c s="4"/>
-      <x:c s="4"/>
+        <x:v>104</x:v>
+      </x:c>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
+        <x:v>106</x:v>
+      </x:c>
+      <x:c s="4" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c s="4"/>
+      <x:c s="4" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
@@ -1555,52 +2503,88 @@
       <x:c s="15" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c s="6" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
       <x:c s="6" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c s="6"/>
       <x:c s="6" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>120</x:v>
+      </x:c>
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
@@ -1613,70 +2597,108 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>138</x:v>
+      </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="1"/>
@@ -1685,9 +2707,14 @@
       </x:c>
       <x:c s="6"/>
       <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>77</x:v>
-      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
@@ -1696,53 +2723,80 @@
       </x:c>
       <x:c s="6"/>
       <x:c s="6" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
@@ -1867,6 +2921,78 @@
       <x:c s="12" t="s">
         <x:v>0</x:v>
       </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="1"/>
@@ -1900,6 +3026,34 @@
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
@@ -1957,6 +3111,30 @@
       <x:c s="5"/>
       <x:c s="5"/>
       <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="2" t="str">
@@ -1967,39 +3145,29 @@
       </x:c>
       <x:c s="7"/>
       <x:c s="7"/>
+      <x:c s="7"/>
       <x:c s="7" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c s="7"/>
-      <x:c s="7"/>
+        <x:v>155</x:v>
+      </x:c>
       <x:c s="7"/>
       <x:c s="7" t="s">
-        <x:v>56</x:v>
-      </x:c>
+        <x:v>156</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7" t="s">
-        <x:v>88</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
-      <x:c s="7"/>
+        <x:v>157</x:v>
+      </x:c>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
@@ -2009,8 +3177,50 @@
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
+        <x:v>158</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
@@ -2020,66 +3230,102 @@
       <x:c s="18" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>177</x:v>
+      </x:c>
       <x:c s="9"/>
     </x:row>
     <x:row ht="60" customHeight="1">
@@ -2087,62 +3333,102 @@
       <x:c s="18" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>181</x:v>
+      </x:c>
       <x:c s="9"/>
       <x:c s="9" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c s="9"/>
       <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>192</x:v>
+      </x:c>
       <x:c s="9"/>
     </x:row>
     <x:row ht="60" customHeight="1">
@@ -2150,56 +3436,92 @@
       <x:c s="18" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c s="9" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c s="9" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>205</x:v>
+      </x:c>
       <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
@@ -2215,51 +3537,83 @@
       </x:c>
       <x:c s="9"/>
       <x:c s="9" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
+        <x:v>206</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>214</x:v>
+      </x:c>
       <x:c s="9"/>
       <x:c s="9"/>
     </x:row>
@@ -2269,25 +3623,53 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>121</x:v>
-      </x:c>
+      <x:c s="9" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c s="9" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
@@ -2356,6 +3738,30 @@
       <x:c s="8"/>
       <x:c s="8"/>
       <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="1" t="str">
@@ -2370,9 +3776,15 @@
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
       <x:c s="4" t="s">
-        <x:v>122</x:v>
-      </x:c>
+        <x:v>218</x:v>
+      </x:c>
+      <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
@@ -2391,8 +3803,9 @@
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4" t="s">
-        <x:v>123</x:v>
-      </x:c>
+        <x:v>219</x:v>
+      </x:c>
+      <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4"/>
@@ -2402,11 +3815,38 @@
       <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4" t="s">
-        <x:v>124</x:v>
-      </x:c>
+        <x:v>220</x:v>
+      </x:c>
+      <x:c s="4"/>
       <x:c s="4"/>
       <x:c s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>221</x:v>
+      </x:c>
+      <x:c s="4" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c s="4"/>
+      <x:c s="4"/>
+      <x:c s="4" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c s="4"/>
+      <x:c s="4" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c s="4" t="s">
+        <x:v>225</x:v>
       </x:c>
       <x:c s="4"/>
       <x:c s="4"/>
@@ -2422,49 +3862,85 @@
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>235</x:v>
+      </x:c>
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
@@ -2474,14 +3950,23 @@
       <x:c s="15" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>131</x:v>
+      <x:c s="6" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>238</x:v>
       </x:c>
       <x:c s="6"/>
       <x:c s="6" t="s">
@@ -2491,41 +3976,70 @@
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>248</x:v>
+      </x:c>
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
@@ -2535,61 +4049,107 @@
       <x:c s="15" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c s="6" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>267</x:v>
+      </x:c>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="1"/>
@@ -2597,47 +4157,83 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
-      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>266</x:v>
+      </x:c>
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
@@ -2656,6 +4252,36 @@
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c s="6" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
+      <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
       <x:c s="6"/>
@@ -2731,6 +4357,30 @@
       <x:c s="5"/>
       <x:c s="5"/>
       <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
+      <x:c s="5"/>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="2" t="str">
@@ -2746,9 +4396,23 @@
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
       <x:c s="7" t="s">
-        <x:v>147</x:v>
-      </x:c>
+        <x:v>277</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
@@ -2774,10 +4438,24 @@
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c s="7"/>
-      <x:c s="7"/>
+        <x:v>278</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7"/>
+      <x:c s="7" t="s">
+        <x:v>280</x:v>
+      </x:c>
       <x:c s="7"/>
       <x:c s="7"/>
       <x:c s="7"/>
@@ -2795,42 +4473,70 @@
       <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>151</x:v>
-      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
     </x:row>
@@ -2846,40 +4552,68 @@
       <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>153</x:v>
-      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
     </x:row>
@@ -2895,42 +4629,66 @@
       <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9" t="s">
-        <x:v>156</x:v>
-      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
     </x:row>
@@ -2978,6 +4736,30 @@
       <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="2"/>
@@ -3023,12 +4805,60 @@
       <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
     </x:row>
     <x:row ht="60" customHeight="1">
       <x:c s="2"/>
       <x:c s="17" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
+      <x:c s="8"/>
       <x:c s="8"/>
       <x:c s="8"/>
       <x:c s="8"/>

--- a/output/all_teachers_orar.xlsx
+++ b/output/all_teachers_orar.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="1" r:id="R025498663fd54f23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="1" r:id="R2f3175dbd9334e87"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,7 +571,7 @@
     <x:t>Fund. progr. (lab) 251/4 IA2604-II</x:t>
   </x:si>
   <x:si>
-    <x:t>) 143/4 DJ2502</x:t>
+    <x:t>Progr. C++ (lab) 143/4 DJ2502</x:t>
   </x:si>
   <x:si>
     <x:t>Geom. dif. (sem) 214/4 M2501</x:t>
@@ -583,7 +583,7 @@
     <x:t>DJ3DU (curs) 423/4</x:t>
   </x:si>
   <x:si>
-    <x:t>) 350/4 DJ2502</x:t>
+    <x:t>DCMIMJ (lab) 350/4 DJ2502</x:t>
   </x:si>
   <x:si>
     <x:t>Sist. de oper. (lab) 145a/4 DU-IA2601</x:t>

--- a/output/all_teachers_orar.xlsx
+++ b/output/all_teachers_orar.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="1" r:id="R2f3175dbd9334e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="1" r:id="R6368b1b1aa464381"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1110,7 +1110,7 @@
         <x:v>Cucu I.</x:v>
       </x:c>
       <x:c s="3" t="str">
-        <x:v>Curmanscii A.</x:v>
+        <x:v>Curmanschii Anton</x:v>
       </x:c>
       <x:c s="3" t="str">
         <x:v>Damian F.</x:v>
